--- a/astro-site/public/dl/coffee-shop-business-plan/coffee-shop-opening-checklist.xlsx
+++ b/astro-site/public/dl/coffee-shop-business-plan/coffee-shop-opening-checklist.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Most health departments want a plan review of your layout and equipment BEFORE you build out; a coffee shop with brunch gets a food establishment permit and an inspection. UK: register your food business with the council at least 28 days before you start (free) and expect a Food Hygiene Rating (1-5) after inspection</t>
+          <t>Most health departments want a plan review of your layout and equipment BEFORE you build out; a coffee shop with brunch gets a food establishment permit and an inspection. UK: register your food business with the council at least 28 days before you start (free) and expect a Food Hygiene Rating (1-5) after inspection in England, Wales and Northern Ireland; Scotland uses FHIS (Pass / Improvement Required)</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Landlords and events often require $1M per occurrence; ask your agent which limits your lease requires</t>
+          <t>Landlords and events often require 1 million per occurrence; ask your agent which limits your lease requires</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Coffee shop: morning shift (6 am-3 pm) and afternoon shift (2 pm-10 pm)</t>
+          <t>Coffee shop: two 8-hour shifts that overlap at midday, for example 7 am-3 pm and 12 pm-8 pm (13 hours open, as on the Staffing tab)</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="45" customHeight="1">
+    <row r="16" ht="74.75" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>☐</t>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Explain to the team how their time records and personal data are handled</t>
+          <t>Tell the team how their time records and personal data are handled</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Hand over the written policy with the hiring paperwork; time-clock and payroll data are personal data, not just a labor requirement</t>
+          <t>There is no single federal rule, but some states protect employee data: if your time clock scans fingerprints or faces, Illinois (BIPA) and a few other states require written notice and consent first. Keep payroll records secure</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/coffee-shop-business-plan/coffee-shop-opening-checklist.xlsx
+++ b/astro-site/public/dl/coffee-shop-business-plan/coffee-shop-opening-checklist.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Most health departments want a plan review of your layout and equipment BEFORE you build out; a coffee shop with brunch gets a food establishment permit and an inspection. UK: register your food business with the council at least 28 days before you start (free) and expect a Food Hygiene Rating (1-5) after inspection in England, Wales and Northern Ireland; Scotland uses FHIS (Pass / Improvement Required)</t>
+          <t>Most health departments want a plan review of your layout and equipment BEFORE you build out; a coffee shop with brunch gets a food establishment permit and an inspection. UK: register your food business with the council at least 28 days before you start (free) and expect a Food Hygiene Rating (0-5) after inspection in England, Wales and Northern Ireland; Scotland uses FHIS (Pass / Improvement Required)</t>
         </is>
       </c>
     </row>
